--- a/data/Formula_1/Formula_1_Grand Prix.xlsx
+++ b/data/Formula_1/Formula_1_Grand Prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA39B77-8438-42D6-9982-9AA84F50ADF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E697C-1940-4433-81A9-6D0A0F6DDCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="823" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="form_1_2000" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6131" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6124" uniqueCount="618">
   <si>
     <t>Round</t>
   </si>
@@ -1898,9 +1898,6 @@
   </si>
   <si>
     <t>George Russell[h]</t>
-  </si>
-  <si>
-    <t>Source:[57][127]</t>
   </si>
 </sst>
 </file>
@@ -6313,6 +6310,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -16381,7 +16389,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
@@ -17331,29 +17339,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
